--- a/data/trans_dic/P2A_senso_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P2A_senso_R-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad sensorial</t>
+          <t>Hogares con personas con limitación por discapacidad sensorial (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,3; 3,48</t>
+          <t>1,36; 3,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,49; 4,16</t>
+          <t>1,51; 4,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,92</t>
+          <t>0,33; 1,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,25; 3,67</t>
+          <t>1,27; 3,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,24</t>
+          <t>0,56; 2,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,53; 4,18</t>
+          <t>1,49; 4,19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,04</t>
+          <t>0,45; 2,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,36; 3,6</t>
+          <t>1,42; 3,72</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,13; 2,54</t>
+          <t>1,14; 2,52</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,75; 3,58</t>
+          <t>1,78; 3,52</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,51; 1,49</t>
+          <t>0,5; 1,51</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,49; 3,09</t>
+          <t>1,56; 3,15</t>
         </is>
       </c>
     </row>
@@ -857,52 +857,52 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,52</t>
+          <t>0,85; 2,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,92; 2,72</t>
+          <t>0,88; 2,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,43; 1,8</t>
+          <t>0,4; 1,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,92; 3,1</t>
+          <t>0,9; 3,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,94; 2,61</t>
+          <t>0,95; 2,63</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,25; 3,13</t>
+          <t>1,23; 3,09</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,17</t>
+          <t>0,63; 2,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,32; 4,06</t>
+          <t>2,25; 3,97</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,11; 2,29</t>
+          <t>1,09; 2,34</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,26; 2,63</t>
+          <t>1,29; 2,55</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,61; 3,15</t>
+          <t>1,59; 3,19</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,57</t>
+          <t>0,55; 2,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,4</t>
+          <t>0,39; 2,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,08</t>
+          <t>0,32; 2,03</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,3; 5,11</t>
+          <t>2,33; 4,96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,81</t>
+          <t>0,78; 2,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,66</t>
+          <t>0,69; 2,58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,76</t>
+          <t>0,33; 1,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,82; 57,02</t>
+          <t>3,86; 61,58</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,18</t>
+          <t>0,86; 2,19</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,02</t>
+          <t>0,71; 1,99</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,58</t>
+          <t>0,47; 1,61</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,61; 43,0</t>
+          <t>3,52; 41,8</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,35</t>
+          <t>0,81; 2,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,81</t>
+          <t>0,89; 2,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,62; 2,18</t>
+          <t>0,67; 2,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,98; 2,68</t>
+          <t>1,03; 2,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,2; 2,93</t>
+          <t>1,21; 2,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,71; 3,82</t>
+          <t>1,73; 3,74</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,57; 1,86</t>
+          <t>0,56; 1,91</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,67; 3,39</t>
+          <t>1,66; 3,27</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,17; 2,29</t>
+          <t>1,17; 2,4</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,58; 2,91</t>
+          <t>1,57; 2,85</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,75; 1,74</t>
+          <t>0,76; 1,78</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,55; 2,77</t>
+          <t>1,57; 2,73</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,16; 2,02</t>
+          <t>1,15; 2,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,27; 2,19</t>
+          <t>1,27; 2,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,69; 1,47</t>
+          <t>0,68; 1,44</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,63; 2,76</t>
+          <t>1,69; 2,87</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,26; 2,17</t>
+          <t>1,28; 2,14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,76; 2,76</t>
+          <t>1,76; 2,74</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,77; 1,47</t>
+          <t>0,75; 1,45</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,79; 25,35</t>
+          <t>2,79; 25,2</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,3; 1,92</t>
+          <t>1,32; 1,91</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,61; 2,32</t>
+          <t>1,62; 2,3</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,79; 1,31</t>
+          <t>0,81; 1,34</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,46; 15,39</t>
+          <t>2,47; 14,69</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad sensorial</t>
+          <t>Hogares con personas con limitación por discapacidad sensorial (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>9036; 24181</t>
+          <t>9414; 24834</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10481; 29249</t>
+          <t>10622; 29293</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2061; 12936</t>
+          <t>2215; 12057</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7943; 23338</t>
+          <t>8055; 23196</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4085; 15404</t>
+          <t>3848; 15474</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10640; 29136</t>
+          <t>10416; 29213</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2808; 13710</t>
+          <t>3051; 13950</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9829; 26148</t>
+          <t>10280; 26973</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>15621; 35162</t>
+          <t>15749; 34854</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>24569; 50199</t>
+          <t>24867; 49286</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6939; 20068</t>
+          <t>6789; 20294</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>20224; 41996</t>
+          <t>21288; 42867</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7998; 24196</t>
+          <t>8140; 24967</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9351; 27682</t>
+          <t>8916; 26313</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4437; 18417</t>
+          <t>4119; 19060</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11032; 37038</t>
+          <t>10781; 36890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9088; 25295</t>
+          <t>9234; 25515</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12867; 32280</t>
+          <t>12722; 31883</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6765; 22608</t>
+          <t>6531; 23691</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>22227; 38923</t>
+          <t>21578; 38075</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21506; 44105</t>
+          <t>21111; 45086</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25873; 53954</t>
+          <t>26487; 52370</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13224; 34436</t>
+          <t>13160; 34492</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>34554; 67858</t>
+          <t>34299; 68665</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3722; 17420</t>
+          <t>3752; 16178</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3015; 18171</t>
+          <t>2959; 17089</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2408; 15772</t>
+          <t>2408; 15415</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16190; 35982</t>
+          <t>16453; 34954</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5436; 19231</t>
+          <t>5335; 18600</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5324; 20674</t>
+          <t>5397; 20059</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2298; 13782</t>
+          <t>2556; 13774</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>35653; 532194</t>
+          <t>36038; 574782</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11258; 29643</t>
+          <t>11670; 29887</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11515; 31065</t>
+          <t>10971; 30501</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7248; 24386</t>
+          <t>7191; 24936</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>59135; 704362</t>
+          <t>57711; 684684</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7451; 22105</t>
+          <t>7670; 22344</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8958; 26585</t>
+          <t>8393; 25113</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5795; 20453</t>
+          <t>6301; 22570</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9093; 24818</t>
+          <t>9519; 25636</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12514; 30420</t>
+          <t>12619; 30937</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17943; 40196</t>
+          <t>18180; 39380</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5954; 19445</t>
+          <t>5875; 19931</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>18291; 37146</t>
+          <t>18141; 35805</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>23090; 45326</t>
+          <t>23117; 47487</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>31628; 58131</t>
+          <t>31303; 57090</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14874; 34517</t>
+          <t>15082; 35346</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>31410; 56037</t>
+          <t>31714; 55164</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>38003; 66259</t>
+          <t>37661; 66661</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>43387; 75044</t>
+          <t>43454; 76525</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>23416; 50009</t>
+          <t>22996; 48808</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>56418; 95588</t>
+          <t>58510; 99242</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>42733; 73473</t>
+          <t>43136; 72447</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>62677; 98308</t>
+          <t>62695; 97628</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>27272; 52016</t>
+          <t>26546; 51329</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>103513; 941132</t>
+          <t>103528; 935404</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>86200; 127504</t>
+          <t>87814; 127417</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>112471; 161895</t>
+          <t>113441; 160581</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>54633; 90956</t>
+          <t>56035; 93225</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>176341; 1103892</t>
+          <t>177115; 1053611</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_senso_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P2A_senso_R-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -717,22 +717,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,36; 3,58</t>
+          <t>1,27; 3,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,51; 4,16</t>
+          <t>1,51; 3,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,79</t>
+          <t>0,4; 1,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,27; 3,65</t>
+          <t>1,19; 3,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -742,37 +742,37 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,49; 4,19</t>
+          <t>1,58; 4,12</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,07</t>
+          <t>0,42; 2,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,42; 3,72</t>
+          <t>1,73; 4,15</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,14; 2,52</t>
+          <t>1,13; 2,44</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,78; 3,52</t>
+          <t>1,86; 3,63</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,51</t>
+          <t>0,54; 1,58</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,56; 3,15</t>
+          <t>1,65; 3,22</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,85; 2,6</t>
+          <t>0,84; 2,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,88; 2,58</t>
+          <t>0,88; 2,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,86</t>
+          <t>0,46; 1,94</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,9; 3,09</t>
+          <t>1,49; 3,75</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,63</t>
+          <t>1,05; 2,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,23; 3,09</t>
+          <t>1,21; 3,12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,27</t>
+          <t>0,62; 2,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,25; 3,97</t>
+          <t>2,38; 4,13</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,09; 2,34</t>
+          <t>1,1; 2,22</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,29; 2,55</t>
+          <t>1,25; 2,47</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,64; 1,67</t>
+          <t>0,67; 1,73</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,59; 3,19</t>
+          <t>2,12; 3,53</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,38</t>
+          <t>0,56; 2,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,26</t>
+          <t>0,4; 2,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,03</t>
+          <t>0,32; 2,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,33; 4,96</t>
+          <t>2,76; 5,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,72</t>
+          <t>0,88; 2,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,58</t>
+          <t>0,72; 2,64</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,75</t>
+          <t>0,39; 1,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,86; 61,58</t>
+          <t>3,57; 6,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,19</t>
+          <t>0,87; 2,22</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,71; 1,99</t>
+          <t>0,8; 2,14</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,61</t>
+          <t>0,47; 1,75</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,52; 41,8</t>
+          <t>3,47; 5,53</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,37</t>
+          <t>0,77; 2,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,65</t>
+          <t>0,89; 2,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,41</t>
+          <t>0,67; 2,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,03; 2,77</t>
+          <t>1,07; 2,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,21; 2,98</t>
+          <t>1,19; 3,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,73; 3,74</t>
+          <t>1,82; 3,89</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,56; 1,91</t>
+          <t>0,59; 1,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,66; 3,27</t>
+          <t>1,98; 3,61</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,17; 2,4</t>
+          <t>1,19; 2,35</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,57; 2,85</t>
+          <t>1,57; 2,95</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,76; 1,78</t>
+          <t>0,75; 1,77</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,57; 2,73</t>
+          <t>1,75; 2,82</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,03</t>
+          <t>1,15; 2,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,27; 2,23</t>
+          <t>1,25; 2,2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,68; 1,44</t>
+          <t>0,67; 1,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,69; 2,87</t>
+          <t>1,96; 3,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,28; 2,14</t>
+          <t>1,27; 2,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,76; 2,74</t>
+          <t>1,72; 2,72</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,75; 1,45</t>
+          <t>0,74; 1,44</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,79; 25,2</t>
+          <t>2,75; 3,79</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,32; 1,91</t>
+          <t>1,32; 1,92</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,62; 2,3</t>
+          <t>1,6; 2,33</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,81; 1,34</t>
+          <t>0,78; 1,31</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,47; 14,69</t>
+          <t>2,55; 3,28</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14004</t>
+          <t>14150</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15727</t>
+          <t>18939</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>29731</t>
+          <t>33089</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>9414; 24834</t>
+          <t>8819; 24048</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10622; 29293</t>
+          <t>10609; 27732</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2215; 12057</t>
+          <t>2682; 13105</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8055; 23196</t>
+          <t>8222; 22793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3848; 15474</t>
+          <t>3874; 15487</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10416; 29213</t>
+          <t>10996; 28729</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3051; 13950</t>
+          <t>2844; 13688</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10280; 26973</t>
+          <t>12733; 30471</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>15749; 34854</t>
+          <t>15642; 33689</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>24867; 49286</t>
+          <t>26079; 50895</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6789; 20294</t>
+          <t>7333; 21280</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>21288; 42867</t>
+          <t>23488; 45893</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>22618</t>
+          <t>24830</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>29631</t>
+          <t>33112</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>52250</t>
+          <t>57942</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8140; 24967</t>
+          <t>8113; 24528</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8916; 26313</t>
+          <t>8978; 26807</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4119; 19060</t>
+          <t>4692; 19838</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10781; 36890</t>
+          <t>15600; 39372</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9234; 25515</t>
+          <t>10189; 26268</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12722; 31883</t>
+          <t>12507; 32240</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6531; 23691</t>
+          <t>6422; 22258</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>21578; 38075</t>
+          <t>25476; 44274</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21111; 45086</t>
+          <t>21304; 42892</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>26487; 52370</t>
+          <t>25618; 50682</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13160; 34492</t>
+          <t>13786; 35821</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>34299; 68665</t>
+          <t>44954; 74852</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24367</t>
+          <t>32206</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>235946</t>
+          <t>38711</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>260312</t>
+          <t>70917</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3752; 16178</t>
+          <t>3766; 16298</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2959; 17089</t>
+          <t>3052; 16268</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2408; 15415</t>
+          <t>2457; 17972</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16453; 34954</t>
+          <t>22125; 47648</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5335; 18600</t>
+          <t>6033; 20033</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5397; 20059</t>
+          <t>5557; 20516</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2556; 13774</t>
+          <t>3037; 14048</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>36038; 574782</t>
+          <t>29020; 50982</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11670; 29887</t>
+          <t>11821; 30198</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10971; 30501</t>
+          <t>12321; 32784</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7191; 24936</t>
+          <t>7228; 27053</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>57711; 684684</t>
+          <t>56004; 89290</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15765</t>
+          <t>16819</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>26150</t>
+          <t>29923</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>41916</t>
+          <t>46743</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7670; 22344</t>
+          <t>7294; 21137</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8393; 25113</t>
+          <t>8433; 26266</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6301; 22570</t>
+          <t>6315; 20370</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9519; 25636</t>
+          <t>10579; 26689</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12619; 30937</t>
+          <t>12335; 31653</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18180; 39380</t>
+          <t>19179; 40920</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5875; 19931</t>
+          <t>6147; 19660</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>18141; 35805</t>
+          <t>22188; 40357</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>23117; 47487</t>
+          <t>23598; 46465</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>31303; 57090</t>
+          <t>31449; 58961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>15082; 35346</t>
+          <t>14936; 35122</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>31714; 55164</t>
+          <t>36834; 59380</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>76755</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>307454</t>
+          <t>120685</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>384209</t>
+          <t>208690</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>37661; 66661</t>
+          <t>37702; 65606</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>43454; 76525</t>
+          <t>42672; 75290</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22996; 48808</t>
+          <t>22904; 50111</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>58510; 99242</t>
+          <t>69106; 110224</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>43136; 72447</t>
+          <t>43055; 73542</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>62695; 97628</t>
+          <t>61273; 96951</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26546; 51329</t>
+          <t>26305; 51035</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>103528; 935404</t>
+          <t>102653; 141561</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>87814; 127417</t>
+          <t>87785; 127834</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>113441; 160581</t>
+          <t>112025; 162776</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>56035; 93225</t>
+          <t>54381; 90609</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>177115; 1053611</t>
+          <t>185026; 238607</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_senso_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P2A_senso_R-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad sensorial (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con personas con alguna limitación por discapacidad sensorial (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad sensorial (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con personas con alguna limitación por discapacidad sensorial (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
